--- a/Lab MB1 B/listado 2.xlsx
+++ b/Lab MB1 B/listado 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Lab MB1 B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEED775-8EA3-4B7F-AAB5-B0A6E5AB4599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50229E13-B45E-4226-A9FC-90B421EBDA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t xml:space="preserve">Semana Congreso </t>
+  </si>
+  <si>
+    <t>HT2 inge</t>
   </si>
 </sst>
 </file>
@@ -414,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -425,22 +428,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,46 +755,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9337005-F0FF-4A3F-B098-783C2B519B7D}">
-  <dimension ref="A4:L80"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A4:N80"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="42.28515625" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" style="11" customWidth="1"/>
-    <col min="7" max="8" width="27.28515625" customWidth="1"/>
-    <col min="9" max="10" width="31.85546875" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="36.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="42.26953125" customWidth="1"/>
+    <col min="8" max="10" width="27.26953125" customWidth="1"/>
+    <col min="11" max="12" width="31.81640625" customWidth="1"/>
+    <col min="13" max="13" width="22.81640625" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="I4" s="5" t="s">
+    <row r="4" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="K4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" s="14" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="I5" s="5" t="s">
+      <c r="N4" s="14"/>
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="K5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,2146 +806,2338 @@
       <c r="E6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="10">
+      <c r="J6" s="4"/>
+      <c r="K6" s="8">
         <v>45911</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K6" s="2">
+      <c r="M6" s="2">
         <v>45930</v>
       </c>
-      <c r="L6" s="2">
+      <c r="N6" s="2">
         <v>45902</v>
       </c>
     </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
+    <row r="7" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>202030174</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6">
-        <v>100</v>
+      <c r="F7">
+        <v>0</v>
       </c>
       <c r="I7">
-        <f>IF(F7&gt;0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <f>IF(G7&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="6">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <f>IF(H7&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>IF(I7&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8">
         <v>202032032</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="7">
-        <v>100</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <f t="shared" ref="I8:I71" si="0">IF(F8&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <f t="shared" ref="J8:J71" si="1">IF(G8&gt;0,1,0)</f>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C9" s="6">
+        <f t="shared" ref="K8:K71" si="0">IF(H8&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ref="L8:L71" si="1">IF(I8&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9">
         <v>202231116</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>85</v>
       </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10">
         <v>202330276</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="6"/>
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="1"/>
+      <c r="F10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C11">
         <v>5</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11">
         <v>202331587</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>85</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="I11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C12">
         <v>6</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12">
         <v>202332049</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="6"/>
-      <c r="I12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="1"/>
+      <c r="F12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C13">
         <v>7</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13">
         <v>202402553</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="6">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>65</v>
       </c>
-      <c r="I13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C14">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14">
         <v>202430271</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6">
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="I14">
         <v>70</v>
       </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C15">
         <v>9</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15">
         <v>202430532</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>65</v>
       </c>
-      <c r="G15" s="6">
+      <c r="I15">
         <v>80</v>
       </c>
-      <c r="I15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="C16">
         <v>10</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16">
         <v>202430589</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="6"/>
-      <c r="I16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
+      <c r="F16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C17">
         <v>11</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17">
         <v>202430602</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>30</v>
       </c>
-      <c r="I17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C18">
         <v>12</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18">
         <v>202430633</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="7">
-        <v>100</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
         <v>50</v>
       </c>
-      <c r="I18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19">
         <v>13</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19">
         <v>202430645</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>75</v>
       </c>
-      <c r="G19" s="6">
+      <c r="I19">
         <v>70</v>
       </c>
-      <c r="I19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C20">
         <v>14</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20">
         <v>202430733</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="7">
-        <v>100</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C21">
         <v>15</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21">
         <v>202430804</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="7">
-        <v>100</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22">
         <v>16</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22">
         <v>202430829</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="H22">
         <v>85</v>
       </c>
-      <c r="G22" s="6">
+      <c r="I22">
         <v>85</v>
       </c>
-      <c r="I22">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C23">
         <v>17</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23">
         <v>202431169</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="7">
-        <v>100</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24">
         <v>18</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24">
         <v>202431502</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="H24">
         <v>90</v>
       </c>
-      <c r="G24" s="6">
+      <c r="I24">
         <v>45</v>
       </c>
-      <c r="I24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
-      <c r="C25" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="7"/>
+      <c r="C25">
         <v>19</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25">
         <v>202431726</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>95</v>
       </c>
-      <c r="G25" s="6">
+      <c r="I25">
         <v>90</v>
       </c>
-      <c r="I25">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C26">
         <v>20</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26">
         <v>202431817</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>15</v>
       </c>
-      <c r="G26" s="6">
+      <c r="I26">
         <v>90</v>
       </c>
-      <c r="I26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C27">
         <v>21</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27">
         <v>202431819</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="H27">
         <v>85</v>
       </c>
-      <c r="G27" s="6">
+      <c r="I27">
         <v>70</v>
       </c>
-      <c r="I27">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28">
         <v>22</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28">
         <v>202431863</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="6">
-        <v>100</v>
+      <c r="F28">
+        <v>0</v>
       </c>
       <c r="I28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C29" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C29">
         <v>23</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29">
         <v>202432080</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="7">
-        <v>100</v>
-      </c>
-      <c r="G29" s="6">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>100</v>
       </c>
       <c r="I29">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C30">
         <v>24</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30">
         <v>202432085</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>95</v>
       </c>
-      <c r="G30" s="6">
+      <c r="I30">
         <v>90</v>
       </c>
-      <c r="I30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
         <v>84</v>
       </c>
       <c r="B31" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31">
         <v>25</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31">
         <v>202432137</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" t="s">
         <v>27</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="6">
-        <v>100</v>
+      <c r="F31">
+        <v>0</v>
       </c>
       <c r="I31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C32" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C32">
         <v>26</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32">
         <v>202530125</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>90</v>
       </c>
-      <c r="G32" s="6">
+      <c r="I32">
         <v>60</v>
       </c>
-      <c r="I32">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33">
         <v>27</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33">
         <v>202530235</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7">
-        <v>100</v>
+      <c r="F33">
+        <v>0</v>
       </c>
       <c r="I33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34">
         <v>28</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34">
         <v>202530265</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="7">
-        <v>100</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="H34">
         <v>100</v>
       </c>
       <c r="I34">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C35" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C35">
         <v>29</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35">
         <v>202530315</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="7">
-        <v>100</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
         <v>50</v>
       </c>
-      <c r="I35">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C36" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C36">
         <v>30</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36">
         <v>202530329</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" t="s">
         <v>32</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>85</v>
       </c>
-      <c r="G36" s="6">
+      <c r="I36">
         <v>65</v>
       </c>
-      <c r="I36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J36">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37">
         <v>31</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37">
         <v>202530349</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>90</v>
       </c>
-      <c r="G37" s="6">
+      <c r="I37">
         <v>60</v>
       </c>
-      <c r="I37">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C38">
         <v>32</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38">
         <v>202530357</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" t="s">
         <v>34</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>65</v>
       </c>
-      <c r="G38" s="6">
+      <c r="I38">
         <v>80</v>
       </c>
-      <c r="I38">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C39" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C39">
         <v>33</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39">
         <v>202530381</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="H39">
         <v>90</v>
       </c>
-      <c r="G39" s="6">
+      <c r="I39">
         <v>45</v>
       </c>
-      <c r="I39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J39">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40">
         <v>34</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40">
         <v>202530434</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" t="s">
         <v>36</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>75</v>
       </c>
-      <c r="G40" s="7">
-        <v>100</v>
-      </c>
       <c r="I40">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J40">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41">
         <v>35</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41">
         <v>202530446</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" t="s">
         <v>37</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>85</v>
       </c>
-      <c r="G41" s="6">
+      <c r="I41">
         <v>80</v>
       </c>
-      <c r="I41">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J41">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C42" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C42">
         <v>36</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42">
         <v>202530522</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" t="s">
         <v>38</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>80</v>
       </c>
-      <c r="G42" s="6">
+      <c r="I42">
         <v>80</v>
       </c>
-      <c r="I42">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J42">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C43" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C43">
         <v>37</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43">
         <v>202530613</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" t="s">
         <v>39</v>
       </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="6"/>
-      <c r="I43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C44" s="6">
+      <c r="F43">
+        <v>100</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C44">
         <v>38</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44">
         <v>202530621</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>60</v>
       </c>
-      <c r="G44" s="7">
+      <c r="I44">
         <v>65</v>
       </c>
-      <c r="I44">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45">
         <v>39</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45">
         <v>202530673</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>95</v>
       </c>
-      <c r="G45" s="6"/>
-      <c r="I45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="K45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C46" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C46">
         <v>40</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46">
         <v>202530674</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>85</v>
       </c>
-      <c r="G46" s="6">
+      <c r="I46">
         <v>70</v>
       </c>
-      <c r="I46">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C47" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C47">
         <v>41</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47">
         <v>202530677</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="6"/>
-      <c r="I47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="1"/>
+      <c r="F47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48">
         <v>42</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48">
         <v>202530728</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>85</v>
       </c>
-      <c r="G48" s="7">
+      <c r="I48">
         <v>50</v>
       </c>
-      <c r="I48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J48">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A49" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49">
         <v>43</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49">
         <v>202530843</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" t="s">
         <v>45</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>85</v>
       </c>
-      <c r="G49" s="7">
+      <c r="I49">
         <v>85</v>
       </c>
-      <c r="I49">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J49">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="6">
+      <c r="K49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C50">
         <v>44</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50">
         <v>202530866</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" t="s">
         <v>46</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>85</v>
       </c>
-      <c r="G50" s="7">
+      <c r="I50">
         <v>55</v>
       </c>
-      <c r="I50">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J50">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A51" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51">
         <v>45</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51">
         <v>202530917</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" t="s">
         <v>47</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="H51">
         <v>95</v>
       </c>
-      <c r="G51" s="6">
+      <c r="I51">
         <v>65</v>
       </c>
-      <c r="I51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J51">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C52">
         <v>46</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52">
         <v>202531013</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" t="s">
         <v>48</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>90</v>
       </c>
-      <c r="G52" s="6">
+      <c r="I52">
         <v>70</v>
       </c>
-      <c r="I52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J52">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C53">
         <v>47</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53">
         <v>202531019</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" t="s">
         <v>49</v>
       </c>
-      <c r="F53" s="7"/>
-      <c r="G53" s="6">
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="I53">
         <v>55</v>
       </c>
-      <c r="I53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C54" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C54">
         <v>48</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54">
         <v>202531089</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" t="s">
         <v>50</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>85</v>
       </c>
-      <c r="G54" s="7">
+      <c r="I54">
         <v>55</v>
       </c>
-      <c r="I54">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J54">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="6">
+      <c r="K54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C55">
         <v>49</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55">
         <v>202531127</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" t="s">
         <v>51</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>85</v>
       </c>
-      <c r="G55" s="7">
+      <c r="I55">
         <v>85</v>
       </c>
-      <c r="I55">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C56">
         <v>50</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56">
         <v>202531213</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" t="s">
         <v>52</v>
       </c>
-      <c r="F56" s="7">
-        <v>100</v>
-      </c>
-      <c r="G56" s="6">
+      <c r="F56">
+        <v>100</v>
+      </c>
+      <c r="H56">
         <v>100</v>
       </c>
       <c r="I56">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J56">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C57">
         <v>51</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57">
         <v>202531219</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" t="s">
         <v>53</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="H57">
         <v>45</v>
       </c>
-      <c r="G57" s="6"/>
-      <c r="I57">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J57">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="K57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C58" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C58">
         <v>52</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58">
         <v>202531289</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" t="s">
         <v>54</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="H58">
         <v>95</v>
       </c>
-      <c r="G58" s="6">
+      <c r="I58">
         <v>85</v>
       </c>
-      <c r="I58">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J58">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A59" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59">
         <v>53</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59">
         <v>202531319</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" t="s">
         <v>55</v>
       </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7">
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="I59">
         <v>50</v>
       </c>
-      <c r="I59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A60" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60">
         <v>54</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60">
         <v>202531351</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" t="s">
         <v>56</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60">
+        <v>100</v>
+      </c>
+      <c r="H60">
         <v>90</v>
       </c>
-      <c r="G60" s="6">
-        <v>100</v>
-      </c>
       <c r="I60">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J60">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A61" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61">
         <v>55</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61">
         <v>202531352</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" t="s">
         <v>57</v>
       </c>
-      <c r="F61" s="7"/>
-      <c r="G61" s="6">
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="I61">
         <v>75</v>
       </c>
-      <c r="I61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C62" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C62">
         <v>56</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62">
         <v>202531384</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" t="s">
         <v>58</v>
       </c>
-      <c r="F62" s="7">
-        <v>100</v>
-      </c>
-      <c r="G62" s="6">
+      <c r="F62">
+        <v>100</v>
+      </c>
+      <c r="H62">
+        <v>100</v>
+      </c>
+      <c r="I62">
         <v>90</v>
       </c>
-      <c r="I62">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J62">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C63" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C63">
         <v>57</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63">
         <v>202531399</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="6"/>
-      <c r="I63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <f t="shared" si="1"/>
+      <c r="F63">
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C64" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C64">
         <v>58</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64">
         <v>202531441</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" t="s">
         <v>60</v>
       </c>
-      <c r="F64" s="7"/>
-      <c r="G64" s="6"/>
-      <c r="I64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <f t="shared" si="1"/>
+      <c r="F64">
         <v>0</v>
       </c>
       <c r="K64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C65" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C65">
         <v>59</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65">
         <v>202531444</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="7"/>
-      <c r="G65" s="6">
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="I65">
         <v>65</v>
       </c>
-      <c r="I65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C66" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C66">
         <v>60</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66">
         <v>202531566</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" t="s">
         <v>62</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="H66">
         <v>75</v>
       </c>
-      <c r="G66" s="6">
+      <c r="I66">
         <v>55</v>
       </c>
-      <c r="I66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J66">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A67" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67">
         <v>61</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67">
         <v>202531611</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" t="s">
         <v>63</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="H67">
         <v>45</v>
       </c>
-      <c r="G67" s="6">
+      <c r="I67">
         <v>75</v>
       </c>
-      <c r="I67">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J67">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C68" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C68">
         <v>62</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68">
         <v>202531645</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" t="s">
         <v>64</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68">
+        <v>100</v>
+      </c>
+      <c r="H68">
         <v>90</v>
       </c>
-      <c r="G68" s="6">
-        <v>100</v>
-      </c>
       <c r="I68">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J68">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C69" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C69">
         <v>63</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69">
         <v>202531663</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" t="s">
         <v>65</v>
       </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="6"/>
-      <c r="I69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <f t="shared" si="1"/>
+      <c r="F69">
         <v>0</v>
       </c>
       <c r="K69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C70" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C70">
         <v>64</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70">
         <v>202531724</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" t="s">
         <v>66</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="H70">
         <v>75</v>
       </c>
-      <c r="G70" s="6">
+      <c r="I70">
         <v>70</v>
       </c>
-      <c r="I70">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J70">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C71" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C71">
         <v>65</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71">
         <v>202531736</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="H71">
         <v>60</v>
       </c>
-      <c r="G71" s="7">
+      <c r="I71">
         <v>65</v>
       </c>
-      <c r="I71">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J71">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="K71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A72" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72">
         <v>66</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72">
         <v>202531778</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="E72" t="s">
         <v>68</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="H72">
         <v>90</v>
       </c>
-      <c r="G72" s="7">
-        <v>100</v>
-      </c>
       <c r="I72">
-        <f t="shared" ref="I72:I79" si="2">IF(F72&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J72">
-        <f t="shared" ref="J72:J79" si="3">IF(G72&gt;0,1,0)</f>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C73" s="6">
+        <f t="shared" ref="K72:K79" si="2">IF(H72&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ref="L72:L79" si="3">IF(I72&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C73">
         <v>67</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73">
         <v>202531844</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="E73" t="s">
         <v>69</v>
       </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="6">
-        <v>100</v>
+      <c r="F73">
+        <v>0</v>
       </c>
       <c r="I73">
+        <v>100</v>
+      </c>
+      <c r="K73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J73">
+      <c r="L73">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C74" s="6">
+      <c r="M73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C74">
         <v>68</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74">
         <v>202531883</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="E74" t="s">
         <v>70</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="H74">
         <v>95</v>
       </c>
-      <c r="G74" s="6">
+      <c r="I74">
         <v>85</v>
       </c>
-      <c r="I74">
+      <c r="K74">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J74">
+      <c r="L74">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C75" s="6">
+      <c r="M74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C75">
         <v>69</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75">
         <v>202531947</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="E75" t="s">
         <v>71</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="H75">
         <v>90</v>
       </c>
-      <c r="G75" s="6">
+      <c r="I75">
         <v>70</v>
       </c>
-      <c r="I75">
+      <c r="K75">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J75">
+      <c r="L75">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="8">
+      <c r="M75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A76" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76">
         <v>70</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76">
         <v>202532062</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="E76" t="s">
         <v>72</v>
       </c>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7">
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="I76">
         <v>20</v>
       </c>
-      <c r="I76">
+      <c r="K76">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J76">
+      <c r="L76">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C77" s="6">
+      <c r="M76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C77">
         <v>71</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77">
         <v>202532079</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="E77" t="s">
         <v>73</v>
       </c>
-      <c r="F77" s="7"/>
-      <c r="G77" s="6"/>
-      <c r="I77">
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="K77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J77">
+      <c r="L77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78">
         <v>72</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78">
         <v>202530466</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" t="s">
         <v>78</v>
       </c>
-      <c r="F78" s="7">
-        <v>100</v>
-      </c>
-      <c r="G78" s="6">
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="H78">
         <v>100</v>
       </c>
       <c r="I78">
+        <v>100</v>
+      </c>
+      <c r="K78">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79">
         <v>73</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79">
         <v>202030192</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E79" t="s">
         <v>80</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="H79">
         <v>85</v>
       </c>
-      <c r="G79" s="6"/>
-      <c r="I79">
+      <c r="K79">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J79">
+      <c r="L79">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C80" s="13" t="s">
+      <c r="M79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C80" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="15">
-        <f>COUNTIF(F7:F79,"&gt;0")</f>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="11">
+        <f>COUNTIF(H7:H79,"&gt;0")</f>
         <v>50</v>
       </c>
-      <c r="G80" s="16">
-        <f>COUNTIF(G7:G79,"&gt;0")</f>
+      <c r="I80" s="12">
+        <f>COUNTIF(I7:I79,"&gt;0")</f>
         <v>60</v>
       </c>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
-      <c r="L80" s="17"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="10"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="M4:N4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Lab MB1 B/listado 2.xlsx
+++ b/Lab MB1 B/listado 2.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50229E13-B45E-4226-A9FC-90B421EBDA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D0004A-BDF6-4A71-92D6-65C1342B93A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
   <si>
     <t>No.</t>
   </si>
@@ -309,7 +309,40 @@
     <t xml:space="preserve">Semana Congreso </t>
   </si>
   <si>
-    <t>HT2 inge</t>
+    <t>HT5 (28/08/2025)</t>
+  </si>
+  <si>
+    <t>HT(12/08/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geometria y ecuaciones </t>
+  </si>
+  <si>
+    <t>Funciones</t>
+  </si>
+  <si>
+    <t>HT(19/08/2025)</t>
+  </si>
+  <si>
+    <t>HT (2/09/2025)</t>
+  </si>
+  <si>
+    <t>Investigacion teorica polinimios</t>
+  </si>
+  <si>
+    <t>TAREA (2/09/2025)</t>
+  </si>
+  <si>
+    <t>HT1 inge (29/07/2025)</t>
+  </si>
+  <si>
+    <t>HT2 inge (1/08/2025)</t>
+  </si>
+  <si>
+    <t>HT3 inge(13/08/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graficas </t>
   </si>
 </sst>
 </file>
@@ -333,6 +366,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
@@ -429,7 +463,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -441,6 +474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,48 +789,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9337005-F0FF-4A3F-B098-783C2B519B7D}">
-  <dimension ref="A4:N80"/>
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A4:T80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.26953125" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="20.1796875" customWidth="1"/>
     <col min="5" max="5" width="36.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="42.26953125" customWidth="1"/>
-    <col min="8" max="10" width="27.26953125" customWidth="1"/>
-    <col min="11" max="12" width="31.81640625" customWidth="1"/>
-    <col min="13" max="13" width="22.81640625" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="22.54296875" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" customWidth="1"/>
+    <col min="8" max="8" width="18.08984375" customWidth="1"/>
+    <col min="9" max="9" width="24.1796875" customWidth="1"/>
+    <col min="10" max="10" width="30.7265625" customWidth="1"/>
+    <col min="11" max="12" width="27.6328125" customWidth="1"/>
+    <col min="13" max="13" width="21.1796875" customWidth="1"/>
+    <col min="14" max="16" width="27.26953125" customWidth="1"/>
+    <col min="17" max="18" width="31.81640625" customWidth="1"/>
+    <col min="19" max="19" width="22.81640625" customWidth="1"/>
+    <col min="20" max="20" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="K4" s="5" t="s">
+    <row r="4" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="Q4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="S4" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="N4" s="14"/>
-    </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="K5" s="5" t="s">
+      <c r="T4" s="13"/>
+    </row>
+    <row r="5" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s">
+        <v>100</v>
+      </c>
+      <c r="M5" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="R5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="S5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="T5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,31 +858,51 @@
       <c r="E6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="4" t="s">
+      <c r="L6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="8">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="7">
         <v>45911</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="R6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="M6" s="2">
+      <c r="S6" s="2">
         <v>45930</v>
       </c>
-      <c r="N6" s="2">
+      <c r="T6" s="2">
         <v>45902</v>
       </c>
     </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C7">
         <v>1</v>
       </c>
@@ -843,22 +915,40 @@
       <c r="F7">
         <v>0</v>
       </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
       <c r="I7">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
       </c>
       <c r="K7">
-        <f>IF(H7&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>IF(I7&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="M7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <f>IF(N7&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f>IF(O7&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>2</v>
       </c>
@@ -869,27 +959,45 @@
         <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
       <c r="K8">
-        <f t="shared" ref="K8:K71" si="0">IF(H8&gt;0,1,0)</f>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L8:L71" si="1">IF(I8&gt;0,1,0)</f>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" ref="Q8:Q71" si="0">IF(N8&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <f t="shared" ref="R8:R71" si="1">IF(O8&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C9">
         <v>3</v>
       </c>
@@ -900,24 +1008,42 @@
         <v>5</v>
       </c>
       <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
       <c r="I9">
         <v>85</v>
       </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
       <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="O9">
+        <v>85</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C10">
         <v>4</v>
       </c>
@@ -930,19 +1056,37 @@
       <c r="F10">
         <v>0</v>
       </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
       <c r="K10">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:14" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C11">
         <v>5</v>
       </c>
@@ -955,22 +1099,40 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>50</v>
+      </c>
+      <c r="K11">
+        <v>90</v>
+      </c>
+      <c r="L11">
+        <v>80</v>
+      </c>
+      <c r="M11">
+        <v>75</v>
+      </c>
+      <c r="N11">
         <v>85</v>
       </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>6</v>
       </c>
@@ -983,19 +1145,37 @@
       <c r="F12">
         <v>0</v>
       </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
       <c r="K12">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>7</v>
       </c>
@@ -1006,24 +1186,42 @@
         <v>9</v>
       </c>
       <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
         <v>0</v>
       </c>
       <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
+        <v>50</v>
+      </c>
+      <c r="O13">
         <v>65</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C14">
         <v>8</v>
       </c>
@@ -1034,24 +1232,42 @@
         <v>10</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>100</v>
       </c>
       <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>70</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C15">
         <v>9</v>
       </c>
@@ -1062,27 +1278,45 @@
         <v>11</v>
       </c>
       <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
         <v>65</v>
       </c>
-      <c r="I15">
+      <c r="O15">
         <v>80</v>
       </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C16">
         <v>10</v>
       </c>
@@ -1095,19 +1329,37 @@
       <c r="F16">
         <v>0</v>
       </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
       <c r="K16">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>11</v>
       </c>
@@ -1120,22 +1372,40 @@
       <c r="F17">
         <v>0</v>
       </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
       <c r="I17">
+        <v>60</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>90</v>
+      </c>
+      <c r="L17">
+        <v>100</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>30</v>
       </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>12</v>
       </c>
@@ -1146,31 +1416,49 @@
         <v>14</v>
       </c>
       <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>50</v>
       </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>50</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="14" t="s">
         <v>85</v>
       </c>
       <c r="C19">
@@ -1183,27 +1471,45 @@
         <v>15</v>
       </c>
       <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
+        <v>85</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
+        <v>70</v>
+      </c>
+      <c r="N19">
         <v>75</v>
       </c>
-      <c r="I19">
+      <c r="O19">
         <v>70</v>
       </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C20">
         <v>14</v>
       </c>
@@ -1214,27 +1520,45 @@
         <v>16</v>
       </c>
       <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
       </c>
       <c r="I20">
+        <v>85</v>
+      </c>
+      <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>15</v>
       </c>
@@ -1245,31 +1569,49 @@
         <v>17</v>
       </c>
       <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
       <c r="K21">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L21">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="14" t="s">
         <v>86</v>
       </c>
       <c r="C22">
@@ -1284,25 +1626,43 @@
       <c r="F22">
         <v>100</v>
       </c>
-      <c r="H22">
-        <v>85</v>
+      <c r="G22">
+        <v>100</v>
       </c>
       <c r="I22">
         <v>85</v>
       </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
       <c r="K22">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="N22">
+        <v>85</v>
+      </c>
+      <c r="O22">
+        <v>85</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C23">
         <v>17</v>
       </c>
@@ -1313,31 +1673,49 @@
         <v>19</v>
       </c>
       <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
       </c>
       <c r="I23">
+        <v>85</v>
+      </c>
+      <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C24">
@@ -1352,26 +1730,44 @@
       <c r="F24">
         <v>100</v>
       </c>
-      <c r="H24">
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24">
+        <v>50</v>
+      </c>
+      <c r="N24">
         <v>90</v>
       </c>
-      <c r="I24">
+      <c r="O24">
         <v>45</v>
       </c>
-      <c r="K24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="7"/>
+      <c r="Q24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B25" s="14"/>
       <c r="C25">
         <v>19</v>
       </c>
@@ -1382,27 +1778,45 @@
         <v>21</v>
       </c>
       <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>75</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>90</v>
+      </c>
+      <c r="N25">
         <v>95</v>
       </c>
-      <c r="I25">
+      <c r="O25">
         <v>90</v>
       </c>
-      <c r="K25">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C26">
         <v>20</v>
       </c>
@@ -1415,25 +1829,43 @@
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
         <v>15</v>
       </c>
-      <c r="I26">
+      <c r="O26">
         <v>90</v>
       </c>
-      <c r="K26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C27">
         <v>21</v>
       </c>
@@ -1444,31 +1876,49 @@
         <v>23</v>
       </c>
       <c r="F27">
-        <v>100</v>
-      </c>
-      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>100</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
         <v>85</v>
       </c>
-      <c r="I27">
+      <c r="O27">
         <v>70</v>
       </c>
-      <c r="K27">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="14" t="s">
         <v>83</v>
       </c>
       <c r="C28">
@@ -1481,24 +1931,42 @@
         <v>24</v>
       </c>
       <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
       </c>
       <c r="K28">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L28">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C29">
         <v>23</v>
       </c>
@@ -1509,27 +1977,45 @@
         <v>25</v>
       </c>
       <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
       </c>
       <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C30">
         <v>24</v>
       </c>
@@ -1540,31 +2026,49 @@
         <v>26</v>
       </c>
       <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>75</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>90</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30">
+        <v>70</v>
+      </c>
+      <c r="N30">
         <v>95</v>
       </c>
-      <c r="I30">
+      <c r="O30">
         <v>90</v>
       </c>
-      <c r="K30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C31">
@@ -1577,24 +2081,42 @@
         <v>27</v>
       </c>
       <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L31">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C32">
         <v>26</v>
       </c>
@@ -1607,29 +2129,47 @@
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>75</v>
+      </c>
+      <c r="K32">
         <v>90</v>
       </c>
-      <c r="I32">
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
+        <v>80</v>
+      </c>
+      <c r="N32">
+        <v>90</v>
+      </c>
+      <c r="O32">
         <v>60</v>
       </c>
-      <c r="K32">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="14" t="s">
         <v>86</v>
       </c>
       <c r="C33">
@@ -1642,28 +2182,46 @@
         <v>29</v>
       </c>
       <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
         <v>0</v>
       </c>
       <c r="I33">
         <v>100</v>
       </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
       <c r="K33">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C34">
@@ -1678,25 +2236,43 @@
       <c r="F34">
         <v>100</v>
       </c>
-      <c r="H34">
+      <c r="G34">
         <v>100</v>
       </c>
       <c r="I34">
         <v>100</v>
       </c>
+      <c r="J34">
+        <v>90</v>
+      </c>
       <c r="K34">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
+        <v>100</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C35">
         <v>29</v>
       </c>
@@ -1707,27 +2283,45 @@
         <v>31</v>
       </c>
       <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
       </c>
       <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>100</v>
+      </c>
+      <c r="M35">
         <v>50</v>
       </c>
-      <c r="K35">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
+        <v>50</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C36">
         <v>30</v>
       </c>
@@ -1738,31 +2332,49 @@
         <v>32</v>
       </c>
       <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
+        <v>95</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
+        <v>70</v>
+      </c>
+      <c r="N36">
         <v>85</v>
       </c>
-      <c r="I36">
+      <c r="O36">
         <v>65</v>
       </c>
-      <c r="K36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L36">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="14" t="s">
         <v>89</v>
       </c>
       <c r="C37">
@@ -1777,25 +2389,43 @@
       <c r="F37">
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>100</v>
+      </c>
+      <c r="J37">
+        <v>75</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
+        <v>100</v>
+      </c>
+      <c r="M37">
+        <v>80</v>
+      </c>
+      <c r="N37">
         <v>90</v>
       </c>
-      <c r="I37">
+      <c r="O37">
         <v>60</v>
       </c>
-      <c r="K37">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L37">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q37">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C38">
         <v>32</v>
       </c>
@@ -1806,27 +2436,45 @@
         <v>34</v>
       </c>
       <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="H38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
+        <v>100</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>100</v>
+      </c>
+      <c r="M38">
+        <v>80</v>
+      </c>
+      <c r="N38">
         <v>65</v>
       </c>
-      <c r="I38">
+      <c r="O38">
         <v>80</v>
       </c>
-      <c r="K38">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q38">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C39">
         <v>33</v>
       </c>
@@ -1839,29 +2487,47 @@
       <c r="F39">
         <v>100</v>
       </c>
-      <c r="H39">
+      <c r="G39">
+        <v>100</v>
+      </c>
+      <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
+        <v>100</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>100</v>
+      </c>
+      <c r="M39">
+        <v>50</v>
+      </c>
+      <c r="N39">
         <v>90</v>
       </c>
-      <c r="I39">
+      <c r="O39">
         <v>45</v>
       </c>
-      <c r="K39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L39">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q39">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C40">
@@ -1874,31 +2540,49 @@
         <v>36</v>
       </c>
       <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="I40">
         <v>75</v>
       </c>
-      <c r="I40">
-        <v>100</v>
+      <c r="J40">
+        <v>55</v>
       </c>
       <c r="K40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L40">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="N40">
+        <v>75</v>
+      </c>
+      <c r="O40">
+        <v>100</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="14" t="s">
         <v>89</v>
       </c>
       <c r="C41">
@@ -1911,27 +2595,45 @@
         <v>37</v>
       </c>
       <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="H41">
+        <v>100</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>100</v>
+      </c>
+      <c r="J41">
+        <v>100</v>
+      </c>
+      <c r="K41">
+        <v>100</v>
+      </c>
+      <c r="L41">
+        <v>100</v>
+      </c>
+      <c r="M41">
+        <v>50</v>
+      </c>
+      <c r="N41">
         <v>85</v>
       </c>
-      <c r="I41">
+      <c r="O41">
         <v>80</v>
       </c>
-      <c r="K41">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L41">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q41">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C42">
         <v>36</v>
       </c>
@@ -1942,27 +2644,45 @@
         <v>38</v>
       </c>
       <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>100</v>
+      </c>
+      <c r="J42">
+        <v>100</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
+        <v>100</v>
+      </c>
+      <c r="M42">
+        <v>50</v>
+      </c>
+      <c r="N42">
         <v>80</v>
       </c>
-      <c r="I42">
+      <c r="O42">
         <v>80</v>
       </c>
-      <c r="K42">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C43">
         <v>37</v>
       </c>
@@ -1973,21 +2693,39 @@
         <v>39</v>
       </c>
       <c r="F43">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
       </c>
       <c r="K43">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C44">
         <v>38</v>
       </c>
@@ -1998,31 +2736,49 @@
         <v>40</v>
       </c>
       <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="H44">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>70</v>
+      </c>
+      <c r="J44">
+        <v>100</v>
+      </c>
+      <c r="K44">
+        <v>100</v>
+      </c>
+      <c r="L44">
+        <v>100</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
         <v>60</v>
       </c>
-      <c r="I44">
+      <c r="O44">
         <v>65</v>
       </c>
-      <c r="K44">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L44">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C45">
@@ -2037,22 +2793,40 @@
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="H45">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>100</v>
+      </c>
+      <c r="M45">
+        <v>70</v>
+      </c>
+      <c r="N45">
         <v>95</v>
       </c>
-      <c r="K45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L45">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q45">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C46">
         <v>40</v>
       </c>
@@ -2065,25 +2839,43 @@
       <c r="F46">
         <v>0</v>
       </c>
-      <c r="H46">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>100</v>
+      </c>
+      <c r="J46">
+        <v>100</v>
+      </c>
+      <c r="K46">
+        <v>90</v>
+      </c>
+      <c r="L46">
+        <v>100</v>
+      </c>
+      <c r="M46">
+        <v>50</v>
+      </c>
+      <c r="N46">
         <v>85</v>
       </c>
-      <c r="I46">
+      <c r="O46">
         <v>70</v>
       </c>
-      <c r="K46">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L46">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R46">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C47">
         <v>41</v>
       </c>
@@ -2094,25 +2886,43 @@
         <v>43</v>
       </c>
       <c r="F47">
+        <v>100</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>100</v>
+      </c>
+      <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L47">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C48">
@@ -2125,31 +2935,49 @@
         <v>44</v>
       </c>
       <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="H48">
+        <v>100</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>100</v>
+      </c>
+      <c r="M48">
+        <v>70</v>
+      </c>
+      <c r="N48">
         <v>85</v>
       </c>
-      <c r="I48">
+      <c r="O48">
         <v>50</v>
       </c>
-      <c r="K48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L48">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q48">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C49">
@@ -2164,25 +2992,43 @@
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="H49">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>100</v>
+      </c>
+      <c r="M49">
+        <v>70</v>
+      </c>
+      <c r="N49">
         <v>85</v>
       </c>
-      <c r="I49">
+      <c r="O49">
         <v>85</v>
       </c>
-      <c r="K49">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L49">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C50">
         <v>44</v>
       </c>
@@ -2193,31 +3039,49 @@
         <v>46</v>
       </c>
       <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="H50">
+        <v>100</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>100</v>
+      </c>
+      <c r="J50">
+        <v>100</v>
+      </c>
+      <c r="K50">
+        <v>90</v>
+      </c>
+      <c r="L50">
+        <v>100</v>
+      </c>
+      <c r="M50">
+        <v>50</v>
+      </c>
+      <c r="N50">
         <v>85</v>
       </c>
-      <c r="I50">
+      <c r="O50">
         <v>55</v>
       </c>
-      <c r="K50">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L50">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q50">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C51">
@@ -2232,25 +3096,43 @@
       <c r="F51">
         <v>0</v>
       </c>
-      <c r="H51">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>75</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
+      </c>
+      <c r="L51">
+        <v>100</v>
+      </c>
+      <c r="M51">
+        <v>90</v>
+      </c>
+      <c r="N51">
         <v>95</v>
       </c>
-      <c r="I51">
+      <c r="O51">
         <v>65</v>
       </c>
-      <c r="K51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L51">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C52">
         <v>46</v>
       </c>
@@ -2261,27 +3143,45 @@
         <v>48</v>
       </c>
       <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="H52">
+        <v>100</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>100</v>
+      </c>
+      <c r="J52">
+        <v>75</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+      <c r="L52">
+        <v>100</v>
+      </c>
+      <c r="M52">
+        <v>100</v>
+      </c>
+      <c r="N52">
         <v>90</v>
       </c>
-      <c r="I52">
+      <c r="O52">
         <v>70</v>
       </c>
-      <c r="K52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L52">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q52">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C53">
         <v>47</v>
       </c>
@@ -2294,22 +3194,40 @@
       <c r="F53">
         <v>0</v>
       </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
       <c r="I53">
+        <v>100</v>
+      </c>
+      <c r="J53">
         <v>55</v>
       </c>
       <c r="K53">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L53">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="O53">
+        <v>55</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C54">
         <v>48</v>
       </c>
@@ -2320,27 +3238,45 @@
         <v>50</v>
       </c>
       <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="H54">
+        <v>100</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>70</v>
+      </c>
+      <c r="J54">
+        <v>100</v>
+      </c>
+      <c r="K54">
+        <v>90</v>
+      </c>
+      <c r="L54">
+        <v>100</v>
+      </c>
+      <c r="M54">
+        <v>50</v>
+      </c>
+      <c r="N54">
         <v>85</v>
       </c>
-      <c r="I54">
+      <c r="O54">
         <v>55</v>
       </c>
-      <c r="K54">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L54">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M54" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C55">
         <v>49</v>
       </c>
@@ -2353,25 +3289,43 @@
       <c r="F55">
         <v>0</v>
       </c>
-      <c r="H55">
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>100</v>
+      </c>
+      <c r="M55">
+        <v>70</v>
+      </c>
+      <c r="N55">
         <v>85</v>
       </c>
-      <c r="I55">
+      <c r="O55">
         <v>85</v>
       </c>
-      <c r="K55">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q55">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C56">
         <v>50</v>
       </c>
@@ -2384,25 +3338,43 @@
       <c r="F56">
         <v>100</v>
       </c>
-      <c r="H56">
+      <c r="G56">
         <v>100</v>
       </c>
       <c r="I56">
         <v>100</v>
       </c>
+      <c r="J56">
+        <v>90</v>
+      </c>
       <c r="K56">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L56">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="N56">
+        <v>100</v>
+      </c>
+      <c r="O56">
+        <v>100</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C57">
         <v>51</v>
       </c>
@@ -2415,22 +3387,40 @@
       <c r="F57">
         <v>0</v>
       </c>
-      <c r="H57">
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>100</v>
+      </c>
+      <c r="L57">
+        <v>80</v>
+      </c>
+      <c r="M57">
+        <v>70</v>
+      </c>
+      <c r="N57">
         <v>45</v>
       </c>
-      <c r="K57">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L57">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q57">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C58">
         <v>52</v>
       </c>
@@ -2441,31 +3431,49 @@
         <v>54</v>
       </c>
       <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
       </c>
       <c r="I58">
         <v>85</v>
       </c>
+      <c r="J58">
+        <v>100</v>
+      </c>
       <c r="K58">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L58">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="N58">
+        <v>95</v>
+      </c>
+      <c r="O58">
+        <v>85</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R58">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C59">
@@ -2478,28 +3486,46 @@
         <v>55</v>
       </c>
       <c r="F59">
+        <v>100</v>
+      </c>
+      <c r="G59">
         <v>0</v>
       </c>
       <c r="I59">
+        <v>75</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>100</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="O59">
         <v>50</v>
       </c>
-      <c r="K59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C60">
@@ -2514,29 +3540,47 @@
       <c r="F60">
         <v>100</v>
       </c>
-      <c r="H60">
+      <c r="G60">
+        <v>100</v>
+      </c>
+      <c r="I60">
+        <v>100</v>
+      </c>
+      <c r="J60">
+        <v>100</v>
+      </c>
+      <c r="K60">
+        <v>100</v>
+      </c>
+      <c r="L60">
+        <v>100</v>
+      </c>
+      <c r="M60">
+        <v>80</v>
+      </c>
+      <c r="N60">
         <v>90</v>
       </c>
-      <c r="I60">
-        <v>100</v>
-      </c>
-      <c r="K60">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L60">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O60">
+        <v>100</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R60">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C61">
@@ -2549,24 +3593,42 @@
         <v>57</v>
       </c>
       <c r="F61">
+        <v>100</v>
+      </c>
+      <c r="G61">
         <v>0</v>
       </c>
       <c r="I61">
+        <v>100</v>
+      </c>
+      <c r="J61">
+        <v>100</v>
+      </c>
+      <c r="K61">
+        <v>100</v>
+      </c>
+      <c r="L61">
+        <v>100</v>
+      </c>
+      <c r="M61">
+        <v>70</v>
+      </c>
+      <c r="O61">
         <v>75</v>
       </c>
-      <c r="K61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C62">
         <v>56</v>
       </c>
@@ -2579,25 +3641,43 @@
       <c r="F62">
         <v>100</v>
       </c>
-      <c r="H62">
+      <c r="G62">
         <v>100</v>
       </c>
       <c r="I62">
+        <v>100</v>
+      </c>
+      <c r="J62">
+        <v>100</v>
+      </c>
+      <c r="K62">
+        <v>100</v>
+      </c>
+      <c r="L62">
+        <v>100</v>
+      </c>
+      <c r="M62">
+        <v>70</v>
+      </c>
+      <c r="N62">
+        <v>100</v>
+      </c>
+      <c r="O62">
         <v>90</v>
       </c>
-      <c r="K62">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L62">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q62">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C63">
         <v>57</v>
       </c>
@@ -2610,19 +3690,37 @@
       <c r="F63">
         <v>0</v>
       </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
       <c r="K63">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L63">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C64">
         <v>58</v>
       </c>
@@ -2635,19 +3733,37 @@
       <c r="F64">
         <v>0</v>
       </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
       <c r="K64">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L64">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C65">
         <v>59</v>
       </c>
@@ -2658,24 +3774,42 @@
         <v>61</v>
       </c>
       <c r="F65">
+        <v>100</v>
+      </c>
+      <c r="G65">
         <v>0</v>
       </c>
       <c r="I65">
+        <v>100</v>
+      </c>
+      <c r="J65">
+        <v>95</v>
+      </c>
+      <c r="K65">
+        <v>100</v>
+      </c>
+      <c r="L65">
+        <v>100</v>
+      </c>
+      <c r="M65">
+        <v>50</v>
+      </c>
+      <c r="O65">
         <v>65</v>
       </c>
-      <c r="K65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C66">
         <v>60</v>
       </c>
@@ -2686,31 +3820,49 @@
         <v>62</v>
       </c>
       <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="H66">
+        <v>100</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>100</v>
+      </c>
+      <c r="J66">
+        <v>85</v>
+      </c>
+      <c r="K66">
+        <v>100</v>
+      </c>
+      <c r="L66">
+        <v>100</v>
+      </c>
+      <c r="M66">
+        <v>70</v>
+      </c>
+      <c r="N66">
         <v>75</v>
       </c>
-      <c r="I66">
+      <c r="O66">
         <v>55</v>
       </c>
-      <c r="K66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L66">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q66">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C67">
@@ -2723,27 +3875,45 @@
         <v>63</v>
       </c>
       <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="H67">
+        <v>100</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>100</v>
+      </c>
+      <c r="L67">
+        <v>100</v>
+      </c>
+      <c r="M67">
+        <v>70</v>
+      </c>
+      <c r="N67">
         <v>45</v>
       </c>
-      <c r="I67">
+      <c r="O67">
         <v>75</v>
       </c>
-      <c r="K67">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L67">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q67">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C68">
         <v>62</v>
       </c>
@@ -2756,25 +3926,43 @@
       <c r="F68">
         <v>100</v>
       </c>
-      <c r="H68">
+      <c r="G68">
+        <v>100</v>
+      </c>
+      <c r="I68">
+        <v>100</v>
+      </c>
+      <c r="J68">
+        <v>100</v>
+      </c>
+      <c r="K68">
+        <v>100</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
         <v>90</v>
       </c>
-      <c r="I68">
-        <v>100</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L68">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O68">
+        <v>100</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C69">
         <v>63</v>
       </c>
@@ -2785,21 +3973,39 @@
         <v>65</v>
       </c>
       <c r="F69">
+        <v>100</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
         <v>0</v>
       </c>
       <c r="K69">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L69">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C70">
         <v>64</v>
       </c>
@@ -2810,27 +4016,45 @@
         <v>66</v>
       </c>
       <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="H70">
+        <v>100</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>40</v>
+      </c>
+      <c r="J70">
+        <v>85</v>
+      </c>
+      <c r="K70">
+        <v>100</v>
+      </c>
+      <c r="L70">
+        <v>100</v>
+      </c>
+      <c r="M70">
+        <v>70</v>
+      </c>
+      <c r="N70">
         <v>75</v>
       </c>
-      <c r="I70">
+      <c r="O70">
         <v>70</v>
       </c>
-      <c r="K70">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L70">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q70">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R70">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C71">
         <v>65</v>
       </c>
@@ -2841,31 +4065,49 @@
         <v>67</v>
       </c>
       <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="H71">
+        <v>100</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>100</v>
+      </c>
+      <c r="K71">
+        <v>100</v>
+      </c>
+      <c r="L71">
+        <v>100</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
         <v>60</v>
       </c>
-      <c r="I71">
+      <c r="O71">
         <v>65</v>
       </c>
-      <c r="K71">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L71">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q71">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C72">
@@ -2878,27 +4120,45 @@
         <v>68</v>
       </c>
       <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="H72">
+        <v>100</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>75</v>
+      </c>
+      <c r="J72">
+        <v>85</v>
+      </c>
+      <c r="K72">
+        <v>100</v>
+      </c>
+      <c r="L72">
+        <v>100</v>
+      </c>
+      <c r="M72">
+        <v>70</v>
+      </c>
+      <c r="N72">
         <v>90</v>
       </c>
-      <c r="I72">
-        <v>100</v>
-      </c>
-      <c r="K72">
-        <f t="shared" ref="K72:K79" si="2">IF(H72&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L72">
-        <f t="shared" ref="L72:L79" si="3">IF(I72&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O72">
+        <v>100</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" ref="Q72:Q79" si="2">IF(N72&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R72">
+        <f t="shared" ref="R72:R79" si="3">IF(O72&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C73">
         <v>67</v>
       </c>
@@ -2909,24 +4169,42 @@
         <v>69</v>
       </c>
       <c r="F73">
+        <v>100</v>
+      </c>
+      <c r="G73">
         <v>0</v>
       </c>
       <c r="I73">
         <v>100</v>
       </c>
+      <c r="J73">
+        <v>100</v>
+      </c>
       <c r="K73">
+        <v>100</v>
+      </c>
+      <c r="L73">
+        <v>100</v>
+      </c>
+      <c r="M73">
+        <v>100</v>
+      </c>
+      <c r="O73">
+        <v>100</v>
+      </c>
+      <c r="Q73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L73">
+      <c r="R73">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C74">
         <v>68</v>
       </c>
@@ -2937,27 +4215,45 @@
         <v>70</v>
       </c>
       <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
       </c>
       <c r="I74">
         <v>85</v>
       </c>
+      <c r="J74">
+        <v>100</v>
+      </c>
       <c r="K74">
+        <v>100</v>
+      </c>
+      <c r="L74">
+        <v>100</v>
+      </c>
+      <c r="M74">
+        <v>90</v>
+      </c>
+      <c r="N74">
+        <v>95</v>
+      </c>
+      <c r="O74">
+        <v>85</v>
+      </c>
+      <c r="Q74">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L74">
+      <c r="R74">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C75">
         <v>69</v>
       </c>
@@ -2968,31 +4264,49 @@
         <v>71</v>
       </c>
       <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="H75">
+        <v>100</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>85</v>
+      </c>
+      <c r="J75">
+        <v>75</v>
+      </c>
+      <c r="K75">
+        <v>100</v>
+      </c>
+      <c r="L75">
+        <v>100</v>
+      </c>
+      <c r="M75">
+        <v>50</v>
+      </c>
+      <c r="N75">
         <v>90</v>
       </c>
-      <c r="I75">
+      <c r="O75">
         <v>70</v>
       </c>
-      <c r="K75">
+      <c r="Q75">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L75">
+      <c r="R75">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C76">
@@ -3007,22 +4321,40 @@
       <c r="F76">
         <v>0</v>
       </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
       <c r="I76">
+        <v>85</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>100</v>
+      </c>
+      <c r="L76">
+        <v>100</v>
+      </c>
+      <c r="M76">
+        <v>50</v>
+      </c>
+      <c r="O76">
         <v>20</v>
       </c>
-      <c r="K76">
+      <c r="Q76">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L76">
+      <c r="R76">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C77">
         <v>71</v>
       </c>
@@ -3035,20 +4367,38 @@
       <c r="F77">
         <v>0</v>
       </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>50</v>
+      </c>
       <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L77">
+      <c r="R77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B78" t="s">
+      <c r="S77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B78" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C78">
@@ -3061,28 +4411,46 @@
         <v>78</v>
       </c>
       <c r="F78">
-        <v>0</v>
-      </c>
-      <c r="H78">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
       </c>
       <c r="I78">
         <v>100</v>
       </c>
+      <c r="J78">
+        <v>100</v>
+      </c>
       <c r="K78">
+        <v>100</v>
+      </c>
+      <c r="L78">
+        <v>100</v>
+      </c>
+      <c r="M78">
+        <v>100</v>
+      </c>
+      <c r="N78">
+        <v>100</v>
+      </c>
+      <c r="O78">
+        <v>100</v>
+      </c>
+      <c r="Q78">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L78">
+      <c r="R78">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B79" t="s">
+      <c r="S78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C79">
@@ -3097,46 +4465,70 @@
       <c r="F79">
         <v>0</v>
       </c>
-      <c r="H79">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>100</v>
+      </c>
+      <c r="K79">
+        <v>100</v>
+      </c>
+      <c r="L79">
+        <v>100</v>
+      </c>
+      <c r="M79">
+        <v>100</v>
+      </c>
+      <c r="N79">
         <v>85</v>
       </c>
-      <c r="K79">
+      <c r="Q79">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L79">
+      <c r="R79">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C80" s="9" t="s">
+      <c r="S79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C80" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="11">
-        <f>COUNTIF(H7:H79,"&gt;0")</f>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="9"/>
+      <c r="N80" s="10">
+        <f>COUNTIF(N7:N79,"&gt;0")</f>
         <v>50</v>
       </c>
-      <c r="I80" s="12">
-        <f>COUNTIF(I7:I79,"&gt;0")</f>
+      <c r="O80" s="11">
+        <f>COUNTIF(O7:O79,"&gt;0")</f>
         <v>60</v>
       </c>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="10"/>
-      <c r="N80" s="13"/>
+      <c r="P80" s="9"/>
+      <c r="Q80" s="9"/>
+      <c r="R80" s="9"/>
+      <c r="S80" s="9"/>
+      <c r="T80" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S4:T4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lab MB1 B/listado 2.xlsx
+++ b/Lab MB1 B/listado 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D0004A-BDF6-4A71-92D6-65C1342B93A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C975520D-B100-4CD9-B1A7-81566B65D8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
@@ -339,10 +339,10 @@
     <t>HT2 inge (1/08/2025)</t>
   </si>
   <si>
-    <t>HT3 inge(13/08/2025)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Graficas </t>
+  </si>
+  <si>
+    <t>HT3  inge(13/08/2025)</t>
   </si>
 </sst>
 </file>
@@ -471,10 +471,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,7 +799,7 @@
     <col min="5" max="5" width="36.1796875" customWidth="1"/>
     <col min="6" max="6" width="22.54296875" customWidth="1"/>
     <col min="7" max="7" width="19.54296875" customWidth="1"/>
-    <col min="8" max="8" width="18.08984375" customWidth="1"/>
+    <col min="8" max="8" width="19.90625" customWidth="1"/>
     <col min="9" max="9" width="24.1796875" customWidth="1"/>
     <col min="10" max="10" width="30.7265625" customWidth="1"/>
     <col min="11" max="12" width="27.6328125" customWidth="1"/>
@@ -817,10 +817,10 @@
       <c r="R4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="T4" s="13"/>
+      <c r="T4" s="14"/>
     </row>
     <row r="5" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I5" t="s">
@@ -833,7 +833,7 @@
         <v>100</v>
       </c>
       <c r="M5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>77</v>
@@ -865,7 +865,7 @@
         <v>103</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>95</v>
@@ -918,6 +918,9 @@
       <c r="G7">
         <v>0</v>
       </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
@@ -964,6 +967,9 @@
       <c r="G8">
         <v>0</v>
       </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
       <c r="I8">
         <v>100</v>
       </c>
@@ -1013,6 +1019,9 @@
       <c r="G9">
         <v>0</v>
       </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
       <c r="I9">
         <v>85</v>
       </c>
@@ -1059,6 +1068,9 @@
       <c r="G10">
         <v>0</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
       <c r="I10">
         <v>0</v>
       </c>
@@ -1102,6 +1114,9 @@
       <c r="G11">
         <v>0</v>
       </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
       <c r="I11">
         <v>0</v>
       </c>
@@ -1148,6 +1163,9 @@
       <c r="G12">
         <v>0</v>
       </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
       <c r="I12">
         <v>0</v>
       </c>
@@ -1191,6 +1209,9 @@
       <c r="G13">
         <v>0</v>
       </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
       <c r="I13">
         <v>60</v>
       </c>
@@ -1237,6 +1258,9 @@
       <c r="G14">
         <v>100</v>
       </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
       <c r="I14">
         <v>100</v>
       </c>
@@ -1283,6 +1307,9 @@
       <c r="G15">
         <v>0</v>
       </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
       <c r="I15">
         <v>100</v>
       </c>
@@ -1332,6 +1359,9 @@
       <c r="G16">
         <v>0</v>
       </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -1375,6 +1405,9 @@
       <c r="G17">
         <v>0</v>
       </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
       <c r="I17">
         <v>60</v>
       </c>
@@ -1421,6 +1454,9 @@
       <c r="G18">
         <v>0</v>
       </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
       <c r="I18">
         <v>100</v>
       </c>
@@ -1458,7 +1494,7 @@
       <c r="A19" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C19">
@@ -1475,6 +1511,9 @@
       </c>
       <c r="G19">
         <v>0</v>
+      </c>
+      <c r="H19">
+        <v>50</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -1525,6 +1564,9 @@
       <c r="G20">
         <v>0</v>
       </c>
+      <c r="H20">
+        <v>50</v>
+      </c>
       <c r="I20">
         <v>85</v>
       </c>
@@ -1574,6 +1616,9 @@
       <c r="G21">
         <v>0</v>
       </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
       <c r="I21">
         <v>100</v>
       </c>
@@ -1611,7 +1656,7 @@
       <c r="A22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>86</v>
       </c>
       <c r="C22">
@@ -1627,6 +1672,9 @@
         <v>100</v>
       </c>
       <c r="G22">
+        <v>100</v>
+      </c>
+      <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
@@ -1678,6 +1726,9 @@
       <c r="G23">
         <v>0</v>
       </c>
+      <c r="H23">
+        <v>50</v>
+      </c>
       <c r="I23">
         <v>85</v>
       </c>
@@ -1715,7 +1766,7 @@
       <c r="A24" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C24">
@@ -1733,6 +1784,9 @@
       <c r="G24">
         <v>100</v>
       </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
       <c r="I24">
         <v>100</v>
       </c>
@@ -1767,7 +1821,7 @@
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B25" s="14"/>
+      <c r="B25" s="13"/>
       <c r="C25">
         <v>19</v>
       </c>
@@ -1782,6 +1836,9 @@
       </c>
       <c r="G25">
         <v>0</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
       </c>
       <c r="I25">
         <v>75</v>
@@ -1832,6 +1889,9 @@
       <c r="G26">
         <v>0</v>
       </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
       <c r="I26">
         <v>0</v>
       </c>
@@ -1881,6 +1941,9 @@
       <c r="G27">
         <v>100</v>
       </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -1918,7 +1981,7 @@
       <c r="A28" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C28">
@@ -1934,6 +1997,9 @@
         <v>100</v>
       </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
@@ -1982,6 +2048,9 @@
       <c r="G29">
         <v>0</v>
       </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -2031,6 +2100,9 @@
       <c r="G30">
         <v>0</v>
       </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
       <c r="I30">
         <v>75</v>
       </c>
@@ -2086,6 +2158,9 @@
       <c r="G31">
         <v>0</v>
       </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
       <c r="I31">
         <v>0</v>
       </c>
@@ -2132,6 +2207,9 @@
       <c r="G32">
         <v>0</v>
       </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
       <c r="I32">
         <v>100</v>
       </c>
@@ -2169,7 +2247,7 @@
       <c r="A33" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>86</v>
       </c>
       <c r="C33">
@@ -2186,6 +2264,9 @@
       </c>
       <c r="G33">
         <v>0</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -2221,7 +2302,7 @@
       <c r="A34" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C34">
@@ -2237,6 +2318,9 @@
         <v>100</v>
       </c>
       <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34">
         <v>100</v>
       </c>
       <c r="I34">
@@ -2288,6 +2372,9 @@
       <c r="G35">
         <v>0</v>
       </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
       <c r="I35">
         <v>100</v>
       </c>
@@ -2337,6 +2424,9 @@
       <c r="G36">
         <v>0</v>
       </c>
+      <c r="H36">
+        <v>100</v>
+      </c>
       <c r="I36">
         <v>100</v>
       </c>
@@ -2374,7 +2464,7 @@
       <c r="A37" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>89</v>
       </c>
       <c r="C37">
@@ -2391,6 +2481,9 @@
       </c>
       <c r="G37">
         <v>0</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -2441,6 +2534,9 @@
       <c r="G38">
         <v>0</v>
       </c>
+      <c r="H38">
+        <v>100</v>
+      </c>
       <c r="I38">
         <v>100</v>
       </c>
@@ -2490,6 +2586,9 @@
       <c r="G39">
         <v>100</v>
       </c>
+      <c r="H39">
+        <v>100</v>
+      </c>
       <c r="I39">
         <v>100</v>
       </c>
@@ -2527,7 +2626,7 @@
       <c r="A40" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C40">
@@ -2544,6 +2643,9 @@
       </c>
       <c r="G40">
         <v>0</v>
+      </c>
+      <c r="H40">
+        <v>100</v>
       </c>
       <c r="I40">
         <v>75</v>
@@ -2582,7 +2684,7 @@
       <c r="A41" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>89</v>
       </c>
       <c r="C41">
@@ -2599,6 +2701,9 @@
       </c>
       <c r="G41">
         <v>0</v>
+      </c>
+      <c r="H41">
+        <v>100</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -2649,6 +2754,9 @@
       <c r="G42">
         <v>0</v>
       </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
       <c r="I42">
         <v>100</v>
       </c>
@@ -2698,6 +2806,9 @@
       <c r="G43">
         <v>100</v>
       </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -2741,6 +2852,9 @@
       <c r="G44">
         <v>0</v>
       </c>
+      <c r="H44">
+        <v>100</v>
+      </c>
       <c r="I44">
         <v>70</v>
       </c>
@@ -2778,7 +2892,7 @@
       <c r="A45" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C45">
@@ -2794,6 +2908,9 @@
         <v>0</v>
       </c>
       <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
@@ -2842,6 +2959,9 @@
       <c r="G46">
         <v>0</v>
       </c>
+      <c r="H46">
+        <v>50</v>
+      </c>
       <c r="I46">
         <v>100</v>
       </c>
@@ -2891,6 +3011,9 @@
       <c r="G47">
         <v>0</v>
       </c>
+      <c r="H47">
+        <v>100</v>
+      </c>
       <c r="I47">
         <v>100</v>
       </c>
@@ -2922,7 +3045,7 @@
       <c r="A48" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C48">
@@ -2939,6 +3062,9 @@
       </c>
       <c r="G48">
         <v>0</v>
+      </c>
+      <c r="H48">
+        <v>100</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2977,7 +3103,7 @@
       <c r="A49" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C49">
@@ -2993,6 +3119,9 @@
         <v>0</v>
       </c>
       <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
@@ -3044,6 +3173,9 @@
       <c r="G50">
         <v>0</v>
       </c>
+      <c r="H50">
+        <v>100</v>
+      </c>
       <c r="I50">
         <v>100</v>
       </c>
@@ -3081,7 +3213,7 @@
       <c r="A51" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C51">
@@ -3098,6 +3230,9 @@
       </c>
       <c r="G51">
         <v>0</v>
+      </c>
+      <c r="H51">
+        <v>50</v>
       </c>
       <c r="I51">
         <v>75</v>
@@ -3148,6 +3283,9 @@
       <c r="G52">
         <v>0</v>
       </c>
+      <c r="H52">
+        <v>100</v>
+      </c>
       <c r="I52">
         <v>100</v>
       </c>
@@ -3197,6 +3335,9 @@
       <c r="G53">
         <v>0</v>
       </c>
+      <c r="H53">
+        <v>100</v>
+      </c>
       <c r="I53">
         <v>100</v>
       </c>
@@ -3243,6 +3384,9 @@
       <c r="G54">
         <v>0</v>
       </c>
+      <c r="H54">
+        <v>100</v>
+      </c>
       <c r="I54">
         <v>70</v>
       </c>
@@ -3292,6 +3436,9 @@
       <c r="G55">
         <v>0</v>
       </c>
+      <c r="H55">
+        <v>100</v>
+      </c>
       <c r="I55">
         <v>0</v>
       </c>
@@ -3341,6 +3488,9 @@
       <c r="G56">
         <v>100</v>
       </c>
+      <c r="H56">
+        <v>100</v>
+      </c>
       <c r="I56">
         <v>100</v>
       </c>
@@ -3390,6 +3540,9 @@
       <c r="G57">
         <v>0</v>
       </c>
+      <c r="H57">
+        <v>100</v>
+      </c>
       <c r="I57">
         <v>0</v>
       </c>
@@ -3436,6 +3589,9 @@
       <c r="G58">
         <v>0</v>
       </c>
+      <c r="H58">
+        <v>100</v>
+      </c>
       <c r="I58">
         <v>85</v>
       </c>
@@ -3473,7 +3629,7 @@
       <c r="A59" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C59">
@@ -3490,6 +3646,9 @@
       </c>
       <c r="G59">
         <v>0</v>
+      </c>
+      <c r="H59">
+        <v>50</v>
       </c>
       <c r="I59">
         <v>75</v>
@@ -3525,7 +3684,7 @@
       <c r="A60" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C60">
@@ -3541,6 +3700,9 @@
         <v>100</v>
       </c>
       <c r="G60">
+        <v>100</v>
+      </c>
+      <c r="H60">
         <v>100</v>
       </c>
       <c r="I60">
@@ -3580,7 +3742,7 @@
       <c r="A61" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C61">
@@ -3597,6 +3759,9 @@
       </c>
       <c r="G61">
         <v>0</v>
+      </c>
+      <c r="H61">
+        <v>100</v>
       </c>
       <c r="I61">
         <v>100</v>
@@ -3644,6 +3809,9 @@
       <c r="G62">
         <v>100</v>
       </c>
+      <c r="H62">
+        <v>50</v>
+      </c>
       <c r="I62">
         <v>100</v>
       </c>
@@ -3693,6 +3861,9 @@
       <c r="G63">
         <v>0</v>
       </c>
+      <c r="H63">
+        <v>50</v>
+      </c>
       <c r="I63">
         <v>0</v>
       </c>
@@ -3736,6 +3907,9 @@
       <c r="G64">
         <v>0</v>
       </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
       <c r="I64">
         <v>0</v>
       </c>
@@ -3779,6 +3953,9 @@
       <c r="G65">
         <v>0</v>
       </c>
+      <c r="H65">
+        <v>100</v>
+      </c>
       <c r="I65">
         <v>100</v>
       </c>
@@ -3825,6 +4002,9 @@
       <c r="G66">
         <v>0</v>
       </c>
+      <c r="H66">
+        <v>100</v>
+      </c>
       <c r="I66">
         <v>100</v>
       </c>
@@ -3862,7 +4042,7 @@
       <c r="A67" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C67">
@@ -3879,6 +4059,9 @@
       </c>
       <c r="G67">
         <v>0</v>
+      </c>
+      <c r="H67">
+        <v>100</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3929,6 +4112,9 @@
       <c r="G68">
         <v>100</v>
       </c>
+      <c r="H68">
+        <v>100</v>
+      </c>
       <c r="I68">
         <v>100</v>
       </c>
@@ -3978,6 +4164,9 @@
       <c r="G69">
         <v>0</v>
       </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
       <c r="I69">
         <v>0</v>
       </c>
@@ -4021,6 +4210,9 @@
       <c r="G70">
         <v>0</v>
       </c>
+      <c r="H70">
+        <v>50</v>
+      </c>
       <c r="I70">
         <v>40</v>
       </c>
@@ -4070,6 +4262,9 @@
       <c r="G71">
         <v>0</v>
       </c>
+      <c r="H71">
+        <v>100</v>
+      </c>
       <c r="I71">
         <v>0</v>
       </c>
@@ -4107,7 +4302,7 @@
       <c r="A72" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C72">
@@ -4124,6 +4319,9 @@
       </c>
       <c r="G72">
         <v>0</v>
+      </c>
+      <c r="H72">
+        <v>100</v>
       </c>
       <c r="I72">
         <v>75</v>
@@ -4174,6 +4372,9 @@
       <c r="G73">
         <v>0</v>
       </c>
+      <c r="H73">
+        <v>100</v>
+      </c>
       <c r="I73">
         <v>100</v>
       </c>
@@ -4220,6 +4421,9 @@
       <c r="G74">
         <v>0</v>
       </c>
+      <c r="H74">
+        <v>100</v>
+      </c>
       <c r="I74">
         <v>85</v>
       </c>
@@ -4269,6 +4473,9 @@
       <c r="G75">
         <v>0</v>
       </c>
+      <c r="H75">
+        <v>100</v>
+      </c>
       <c r="I75">
         <v>85</v>
       </c>
@@ -4306,7 +4513,7 @@
       <c r="A76" s="6">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C76">
@@ -4323,6 +4530,9 @@
       </c>
       <c r="G76">
         <v>0</v>
+      </c>
+      <c r="H76">
+        <v>100</v>
       </c>
       <c r="I76">
         <v>85</v>
@@ -4370,6 +4580,9 @@
       <c r="G77">
         <v>0</v>
       </c>
+      <c r="H77">
+        <v>100</v>
+      </c>
       <c r="I77">
         <v>0</v>
       </c>
@@ -4416,6 +4629,9 @@
       <c r="G78">
         <v>0</v>
       </c>
+      <c r="H78">
+        <v>100</v>
+      </c>
       <c r="I78">
         <v>100</v>
       </c>
@@ -4467,6 +4683,9 @@
       </c>
       <c r="G79">
         <v>0</v>
+      </c>
+      <c r="H79">
+        <v>50</v>
       </c>
       <c r="I79">
         <v>0</v>

--- a/Lab MB1 B/listado 2.xlsx
+++ b/Lab MB1 B/listado 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C975520D-B100-4CD9-B1A7-81566B65D8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FAE6E5-0916-4E81-9BE6-2E272E036C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
   <si>
     <t>No.</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>HT3  inge(13/08/2025)</t>
+  </si>
+  <si>
+    <t>HT4  inge(29/08/2025)</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9337005-F0FF-4A3F-B098-783C2B519B7D}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A4:T80"/>
+  <dimension ref="A4:U80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="29.26953125" style="1" customWidth="1"/>
@@ -799,56 +802,56 @@
     <col min="5" max="5" width="36.1796875" customWidth="1"/>
     <col min="6" max="6" width="22.54296875" customWidth="1"/>
     <col min="7" max="7" width="19.54296875" customWidth="1"/>
-    <col min="8" max="8" width="19.90625" customWidth="1"/>
-    <col min="9" max="9" width="24.1796875" customWidth="1"/>
-    <col min="10" max="10" width="30.7265625" customWidth="1"/>
-    <col min="11" max="12" width="27.6328125" customWidth="1"/>
-    <col min="13" max="13" width="21.1796875" customWidth="1"/>
-    <col min="14" max="16" width="27.26953125" customWidth="1"/>
-    <col min="17" max="18" width="31.81640625" customWidth="1"/>
-    <col min="19" max="19" width="22.81640625" customWidth="1"/>
-    <col min="20" max="20" width="18.54296875" customWidth="1"/>
+    <col min="8" max="9" width="19.90625" customWidth="1"/>
+    <col min="10" max="10" width="24.1796875" customWidth="1"/>
+    <col min="11" max="11" width="30.7265625" customWidth="1"/>
+    <col min="12" max="13" width="27.6328125" customWidth="1"/>
+    <col min="14" max="14" width="21.1796875" customWidth="1"/>
+    <col min="15" max="17" width="27.26953125" customWidth="1"/>
+    <col min="18" max="19" width="31.81640625" customWidth="1"/>
+    <col min="20" max="20" width="22.81640625" customWidth="1"/>
+    <col min="21" max="21" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="Q4" s="5" t="s">
-        <v>75</v>
-      </c>
+    <row r="4" spans="3:21" x14ac:dyDescent="0.35">
       <c r="R4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="14" t="s">
+      <c r="S4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="T4" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="T4" s="14"/>
-    </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="I5" t="s">
+      <c r="U4" s="14"/>
+    </row>
+    <row r="5" spans="3:21" x14ac:dyDescent="0.35">
+      <c r="J5" t="s">
         <v>96</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>97</v>
       </c>
-      <c r="L5" t="s">
-        <v>100</v>
-      </c>
       <c r="M5" t="s">
+        <v>100</v>
+      </c>
+      <c r="N5" t="s">
         <v>104</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="R5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="T5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="U5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,41 +871,44 @@
         <v>105</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="7">
+      <c r="Q6" s="4"/>
+      <c r="R6" s="7">
         <v>45911</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="S6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>45930</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>45902</v>
       </c>
     </row>
-    <row r="7" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C7">
         <v>1</v>
       </c>
@@ -931,27 +937,30 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <f>IF(N7&gt;0,1,0)</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
       </c>
       <c r="R7">
         <f>IF(O7&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="S7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f>IF(P7&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>2</v>
       </c>
@@ -983,27 +992,30 @@
         <v>100</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
         <v>80</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
       <c r="O8">
         <v>100</v>
       </c>
-      <c r="Q8">
-        <f t="shared" ref="Q8:Q71" si="0">IF(N8&gt;0,1,0)</f>
-        <v>1</v>
+      <c r="P8">
+        <v>100</v>
       </c>
       <c r="R8">
-        <f t="shared" ref="R8:R71" si="1">IF(O8&gt;0,1,0)</f>
+        <f t="shared" ref="R8:R71" si="0">IF(O8&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="S8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" ref="S8:S71" si="1">IF(P8&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C9">
         <v>3</v>
       </c>
@@ -1023,11 +1035,11 @@
         <v>100</v>
       </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>85</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
       <c r="K9">
         <v>100</v>
       </c>
@@ -1035,24 +1047,27 @@
         <v>100</v>
       </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
         <v>70</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>85</v>
       </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C10">
         <v>4</v>
       </c>
@@ -1086,19 +1101,22 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="Q10">
-        <f t="shared" si="0"/>
+      <c r="N10">
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C11">
         <v>5</v>
       </c>
@@ -1118,36 +1136,39 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>50</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>90</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>80</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>75</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>85</v>
       </c>
-      <c r="Q11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R11">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>6</v>
       </c>
@@ -1181,19 +1202,22 @@
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="Q12">
-        <f t="shared" si="0"/>
+      <c r="N12">
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>7</v>
       </c>
@@ -1213,36 +1237,39 @@
         <v>100</v>
       </c>
       <c r="I13">
+        <v>90</v>
+      </c>
+      <c r="J13">
         <v>60</v>
       </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
       <c r="K13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>50</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>65</v>
       </c>
-      <c r="Q13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R13">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C14">
         <v>8</v>
       </c>
@@ -1262,13 +1289,13 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1276,22 +1303,25 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="O14">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>70</v>
       </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R14">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C15">
         <v>9</v>
       </c>
@@ -1326,24 +1356,27 @@
         <v>100</v>
       </c>
       <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
         <v>65</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>80</v>
       </c>
-      <c r="Q15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C16">
         <v>10</v>
       </c>
@@ -1363,33 +1396,36 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
         <v>80</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>70</v>
       </c>
-      <c r="Q16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>11</v>
       </c>
@@ -1409,36 +1445,39 @@
         <v>100</v>
       </c>
       <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>60</v>
       </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
       <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>90</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="P17">
         <v>30</v>
       </c>
-      <c r="Q17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R17">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>12</v>
       </c>
@@ -1470,27 +1509,30 @@
         <v>100</v>
       </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
         <v>50</v>
       </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>50</v>
       </c>
-      <c r="Q18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -1516,39 +1558,42 @@
         <v>50</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
         <v>85</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
         <v>70</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>75</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>70</v>
       </c>
-      <c r="Q19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C20">
         <v>14</v>
       </c>
@@ -1568,11 +1613,11 @@
         <v>50</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>85</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
         <v>100</v>
       </c>
@@ -1580,27 +1625,30 @@
         <v>100</v>
       </c>
       <c r="M20">
+        <v>100</v>
+      </c>
+      <c r="N20">
         <v>50</v>
       </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
       <c r="O20">
         <v>100</v>
       </c>
-      <c r="Q20">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P20">
+        <v>100</v>
       </c>
       <c r="R20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>15</v>
       </c>
@@ -1620,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -1632,27 +1680,30 @@
         <v>100</v>
       </c>
       <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
         <v>80</v>
       </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
       <c r="O21">
         <v>100</v>
       </c>
-      <c r="Q21">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P21">
+        <v>100</v>
       </c>
       <c r="R21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>90</v>
       </c>
@@ -1678,11 +1729,11 @@
         <v>100</v>
       </c>
       <c r="I22">
+        <v>90</v>
+      </c>
+      <c r="J22">
         <v>85</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
         <v>100</v>
       </c>
@@ -1690,27 +1741,30 @@
         <v>100</v>
       </c>
       <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>70</v>
-      </c>
-      <c r="N22">
-        <v>85</v>
       </c>
       <c r="O22">
         <v>85</v>
       </c>
-      <c r="Q22">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P22">
+        <v>85</v>
       </c>
       <c r="R22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C23">
         <v>17</v>
       </c>
@@ -1730,11 +1784,11 @@
         <v>50</v>
       </c>
       <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>85</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
       <c r="K23">
         <v>100</v>
       </c>
@@ -1742,27 +1796,30 @@
         <v>100</v>
       </c>
       <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
         <v>50</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
       <c r="O23">
         <v>100</v>
       </c>
-      <c r="Q23">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P23">
+        <v>100</v>
       </c>
       <c r="R23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -1800,27 +1857,30 @@
         <v>100</v>
       </c>
       <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
         <v>50</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>90</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>45</v>
       </c>
-      <c r="Q24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B25" s="13"/>
       <c r="C25">
         <v>19</v>
@@ -1841,11 +1901,11 @@
         <v>100</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>75</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
       <c r="K25">
         <v>100</v>
       </c>
@@ -1853,27 +1913,30 @@
         <v>100</v>
       </c>
       <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
         <v>90</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>95</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>90</v>
       </c>
-      <c r="Q25">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C26">
         <v>20</v>
       </c>
@@ -1893,39 +1956,42 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
         <v>15</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>90</v>
       </c>
-      <c r="Q26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C27">
         <v>21</v>
       </c>
@@ -1948,36 +2014,39 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
         <v>85</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>70</v>
       </c>
-      <c r="Q27">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -2003,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2012,27 +2081,30 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>100</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>100</v>
       </c>
       <c r="R28">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C29">
         <v>23</v>
       </c>
@@ -2055,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -2064,27 +2136,30 @@
         <v>100</v>
       </c>
       <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
         <v>70</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
       <c r="O29">
         <v>100</v>
       </c>
-      <c r="Q29">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P29">
+        <v>100</v>
       </c>
       <c r="R29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C30">
         <v>24</v>
       </c>
@@ -2104,39 +2179,42 @@
         <v>100</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>75</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>90</v>
       </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
       <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
         <v>70</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>95</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>90</v>
       </c>
-      <c r="Q30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R30">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>84</v>
       </c>
@@ -2162,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2176,22 +2254,25 @@
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
-      <c r="Q31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>100</v>
       </c>
       <c r="R31">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C32">
         <v>26</v>
       </c>
@@ -2214,36 +2295,39 @@
         <v>100</v>
       </c>
       <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
         <v>75</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>90</v>
       </c>
-      <c r="L32">
-        <v>100</v>
-      </c>
       <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
         <v>80</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>90</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>60</v>
       </c>
-      <c r="Q32">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R32">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>90</v>
       </c>
@@ -2283,22 +2367,25 @@
       <c r="M33">
         <v>100</v>
       </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
-      <c r="Q33">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="P33">
+        <v>100</v>
       </c>
       <c r="R33">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2327,36 +2414,39 @@
         <v>100</v>
       </c>
       <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
         <v>90</v>
       </c>
-      <c r="K34">
-        <v>100</v>
-      </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
+        <v>100</v>
+      </c>
+      <c r="N34">
         <v>70</v>
       </c>
-      <c r="N34">
-        <v>100</v>
-      </c>
       <c r="O34">
         <v>100</v>
       </c>
-      <c r="Q34">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P34">
+        <v>100</v>
       </c>
       <c r="R34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C35">
         <v>29</v>
       </c>
@@ -2388,27 +2478,30 @@
         <v>100</v>
       </c>
       <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
         <v>50</v>
       </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
       <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
         <v>50</v>
       </c>
-      <c r="Q35">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C36">
         <v>30</v>
       </c>
@@ -2428,39 +2521,42 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
         <v>95</v>
       </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
       <c r="L36">
         <v>100</v>
       </c>
       <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
         <v>70</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>85</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>65</v>
       </c>
-      <c r="Q36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2489,36 +2585,39 @@
         <v>100</v>
       </c>
       <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
         <v>75</v>
       </c>
-      <c r="K37">
-        <v>100</v>
-      </c>
       <c r="L37">
         <v>100</v>
       </c>
       <c r="M37">
+        <v>100</v>
+      </c>
+      <c r="N37">
         <v>80</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>90</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>60</v>
       </c>
-      <c r="Q37">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C38">
         <v>32</v>
       </c>
@@ -2550,27 +2649,30 @@
         <v>100</v>
       </c>
       <c r="M38">
+        <v>100</v>
+      </c>
+      <c r="N38">
         <v>80</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>65</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>80</v>
       </c>
-      <c r="Q38">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C39">
         <v>33</v>
       </c>
@@ -2602,27 +2704,30 @@
         <v>100</v>
       </c>
       <c r="M39">
+        <v>100</v>
+      </c>
+      <c r="N39">
         <v>50</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>90</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>45</v>
       </c>
-      <c r="Q39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2648,39 +2753,42 @@
         <v>100</v>
       </c>
       <c r="I40">
+        <v>90</v>
+      </c>
+      <c r="J40">
         <v>75</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>55</v>
       </c>
-      <c r="K40">
-        <v>100</v>
-      </c>
       <c r="L40">
         <v>100</v>
       </c>
       <c r="M40">
+        <v>100</v>
+      </c>
+      <c r="N40">
         <v>90</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>75</v>
       </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
-      <c r="Q40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P40">
+        <v>100</v>
       </c>
       <c r="R40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2706,7 +2814,7 @@
         <v>100</v>
       </c>
       <c r="I41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J41">
         <v>100</v>
@@ -2718,27 +2826,30 @@
         <v>100</v>
       </c>
       <c r="M41">
+        <v>100</v>
+      </c>
+      <c r="N41">
         <v>50</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>85</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>80</v>
       </c>
-      <c r="Q41">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C42">
         <v>36</v>
       </c>
@@ -2758,7 +2869,7 @@
         <v>100</v>
       </c>
       <c r="I42">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <v>100</v>
@@ -2770,27 +2881,30 @@
         <v>100</v>
       </c>
       <c r="M42">
+        <v>100</v>
+      </c>
+      <c r="N42">
         <v>50</v>
-      </c>
-      <c r="N42">
-        <v>80</v>
       </c>
       <c r="O42">
         <v>80</v>
       </c>
-      <c r="Q42">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P42">
+        <v>80</v>
       </c>
       <c r="R42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C43">
         <v>37</v>
       </c>
@@ -2824,19 +2938,22 @@
       <c r="M43">
         <v>0</v>
       </c>
-      <c r="Q43">
-        <f t="shared" si="0"/>
+      <c r="N43">
         <v>0</v>
       </c>
       <c r="R43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C44">
         <v>38</v>
       </c>
@@ -2856,11 +2973,11 @@
         <v>100</v>
       </c>
       <c r="I44">
+        <v>90</v>
+      </c>
+      <c r="J44">
         <v>70</v>
       </c>
-      <c r="J44">
-        <v>100</v>
-      </c>
       <c r="K44">
         <v>100</v>
       </c>
@@ -2868,27 +2985,30 @@
         <v>100</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
         <v>60</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>65</v>
       </c>
-      <c r="Q44">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2914,36 +3034,39 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <v>100</v>
       </c>
       <c r="M45">
+        <v>100</v>
+      </c>
+      <c r="N45">
         <v>70</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>95</v>
       </c>
-      <c r="Q45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R45">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="S45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C46">
         <v>40</v>
       </c>
@@ -2963,39 +3086,42 @@
         <v>50</v>
       </c>
       <c r="I46">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>100</v>
       </c>
       <c r="K46">
+        <v>100</v>
+      </c>
+      <c r="L46">
         <v>90</v>
       </c>
-      <c r="L46">
-        <v>100</v>
-      </c>
       <c r="M46">
+        <v>100</v>
+      </c>
+      <c r="N46">
         <v>50</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>85</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>70</v>
       </c>
-      <c r="Q46">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C47">
         <v>41</v>
       </c>
@@ -3015,33 +3141,36 @@
         <v>100</v>
       </c>
       <c r="I47">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K47">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
-      <c r="Q47">
-        <f t="shared" si="0"/>
+      <c r="N47">
         <v>0</v>
       </c>
       <c r="R47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3076,30 +3205,33 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48">
+        <v>100</v>
+      </c>
+      <c r="N48">
         <v>70</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>85</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>50</v>
       </c>
-      <c r="Q48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3134,30 +3266,33 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M49">
+        <v>100</v>
+      </c>
+      <c r="N49">
         <v>70</v>
-      </c>
-      <c r="N49">
-        <v>85</v>
       </c>
       <c r="O49">
         <v>85</v>
       </c>
-      <c r="Q49">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P49">
+        <v>85</v>
       </c>
       <c r="R49">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C50">
         <v>44</v>
       </c>
@@ -3177,39 +3312,42 @@
         <v>100</v>
       </c>
       <c r="I50">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J50">
         <v>100</v>
       </c>
       <c r="K50">
+        <v>100</v>
+      </c>
+      <c r="L50">
         <v>90</v>
       </c>
-      <c r="L50">
-        <v>100</v>
-      </c>
       <c r="M50">
+        <v>100</v>
+      </c>
+      <c r="N50">
         <v>50</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>85</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>55</v>
       </c>
-      <c r="Q50">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3235,39 +3373,42 @@
         <v>50</v>
       </c>
       <c r="I51">
+        <v>100</v>
+      </c>
+      <c r="J51">
         <v>75</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
       <c r="K51">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L51">
         <v>100</v>
       </c>
       <c r="M51">
+        <v>100</v>
+      </c>
+      <c r="N51">
         <v>90</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>95</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>65</v>
       </c>
-      <c r="Q51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C52">
         <v>46</v>
       </c>
@@ -3287,14 +3428,14 @@
         <v>100</v>
       </c>
       <c r="I52">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J52">
+        <v>100</v>
+      </c>
+      <c r="K52">
         <v>75</v>
       </c>
-      <c r="K52">
-        <v>100</v>
-      </c>
       <c r="L52">
         <v>100</v>
       </c>
@@ -3302,24 +3443,27 @@
         <v>100</v>
       </c>
       <c r="N52">
+        <v>100</v>
+      </c>
+      <c r="O52">
         <v>90</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>70</v>
       </c>
-      <c r="Q52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C53">
         <v>47</v>
       </c>
@@ -3339,36 +3483,39 @@
         <v>100</v>
       </c>
       <c r="I53">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J53">
+        <v>100</v>
+      </c>
+      <c r="K53">
         <v>55</v>
       </c>
-      <c r="K53">
-        <v>100</v>
-      </c>
       <c r="L53">
         <v>100</v>
       </c>
       <c r="M53">
+        <v>100</v>
+      </c>
+      <c r="N53">
         <v>95</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>55</v>
       </c>
-      <c r="Q53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R53">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C54">
         <v>48</v>
       </c>
@@ -3388,39 +3535,42 @@
         <v>100</v>
       </c>
       <c r="I54">
+        <v>90</v>
+      </c>
+      <c r="J54">
         <v>70</v>
       </c>
-      <c r="J54">
-        <v>100</v>
-      </c>
       <c r="K54">
+        <v>100</v>
+      </c>
+      <c r="L54">
         <v>90</v>
       </c>
-      <c r="L54">
-        <v>100</v>
-      </c>
       <c r="M54">
+        <v>100</v>
+      </c>
+      <c r="N54">
         <v>50</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>85</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>55</v>
       </c>
-      <c r="Q54">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R54">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S54" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C55">
         <v>49</v>
       </c>
@@ -3449,30 +3599,33 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55">
+        <v>100</v>
+      </c>
+      <c r="N55">
         <v>70</v>
-      </c>
-      <c r="N55">
-        <v>85</v>
       </c>
       <c r="O55">
         <v>85</v>
       </c>
-      <c r="Q55">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P55">
+        <v>85</v>
       </c>
       <c r="R55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C56">
         <v>50</v>
       </c>
@@ -3492,39 +3645,42 @@
         <v>100</v>
       </c>
       <c r="I56">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J56">
+        <v>100</v>
+      </c>
+      <c r="K56">
         <v>90</v>
       </c>
-      <c r="K56">
-        <v>100</v>
-      </c>
       <c r="L56">
         <v>100</v>
       </c>
       <c r="M56">
+        <v>100</v>
+      </c>
+      <c r="N56">
         <v>80</v>
       </c>
-      <c r="N56">
-        <v>100</v>
-      </c>
       <c r="O56">
         <v>100</v>
       </c>
-      <c r="Q56">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P56">
+        <v>100</v>
       </c>
       <c r="R56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C57">
         <v>51</v>
       </c>
@@ -3544,36 +3700,39 @@
         <v>100</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57">
+        <v>100</v>
+      </c>
+      <c r="M57">
         <v>80</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>70</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>45</v>
       </c>
-      <c r="Q57">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R57">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="S57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C58">
         <v>52</v>
       </c>
@@ -3593,11 +3752,11 @@
         <v>100</v>
       </c>
       <c r="I58">
+        <v>100</v>
+      </c>
+      <c r="J58">
         <v>85</v>
       </c>
-      <c r="J58">
-        <v>100</v>
-      </c>
       <c r="K58">
         <v>100</v>
       </c>
@@ -3608,24 +3767,27 @@
         <v>100</v>
       </c>
       <c r="N58">
+        <v>100</v>
+      </c>
+      <c r="O58">
         <v>95</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>85</v>
       </c>
-      <c r="Q58">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3651,36 +3813,39 @@
         <v>50</v>
       </c>
       <c r="I59">
+        <v>100</v>
+      </c>
+      <c r="J59">
         <v>75</v>
       </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
       <c r="K59">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
-      <c r="O59">
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="P59">
         <v>50</v>
       </c>
-      <c r="Q59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R59">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3706,7 +3871,7 @@
         <v>100</v>
       </c>
       <c r="I60">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J60">
         <v>100</v>
@@ -3718,27 +3883,30 @@
         <v>100</v>
       </c>
       <c r="M60">
+        <v>100</v>
+      </c>
+      <c r="N60">
         <v>80</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>90</v>
       </c>
-      <c r="O60">
-        <v>100</v>
-      </c>
-      <c r="Q60">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P60">
+        <v>100</v>
       </c>
       <c r="R60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3776,24 +3944,27 @@
         <v>100</v>
       </c>
       <c r="M61">
+        <v>100</v>
+      </c>
+      <c r="N61">
         <v>70</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>75</v>
       </c>
-      <c r="Q61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R61">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C62">
         <v>56</v>
       </c>
@@ -3813,7 +3984,7 @@
         <v>50</v>
       </c>
       <c r="I62">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J62">
         <v>100</v>
@@ -3825,27 +3996,30 @@
         <v>100</v>
       </c>
       <c r="M62">
+        <v>100</v>
+      </c>
+      <c r="N62">
         <v>70</v>
       </c>
-      <c r="N62">
-        <v>100</v>
-      </c>
       <c r="O62">
+        <v>100</v>
+      </c>
+      <c r="P62">
         <v>90</v>
       </c>
-      <c r="Q62">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C63">
         <v>57</v>
       </c>
@@ -3879,19 +4053,22 @@
       <c r="M63">
         <v>0</v>
       </c>
-      <c r="Q63">
-        <f t="shared" si="0"/>
+      <c r="N63">
         <v>0</v>
       </c>
       <c r="R63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C64">
         <v>58</v>
       </c>
@@ -3925,19 +4102,22 @@
       <c r="M64">
         <v>0</v>
       </c>
-      <c r="Q64">
-        <f t="shared" si="0"/>
+      <c r="N64">
         <v>0</v>
       </c>
       <c r="R64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C65">
         <v>59</v>
       </c>
@@ -3957,36 +4137,39 @@
         <v>100</v>
       </c>
       <c r="I65">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J65">
+        <v>100</v>
+      </c>
+      <c r="K65">
         <v>95</v>
       </c>
-      <c r="K65">
-        <v>100</v>
-      </c>
       <c r="L65">
         <v>100</v>
       </c>
       <c r="M65">
+        <v>100</v>
+      </c>
+      <c r="N65">
         <v>50</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>65</v>
       </c>
-      <c r="Q65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R65">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C66">
         <v>60</v>
       </c>
@@ -4006,39 +4189,42 @@
         <v>100</v>
       </c>
       <c r="I66">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J66">
+        <v>100</v>
+      </c>
+      <c r="K66">
         <v>85</v>
       </c>
-      <c r="K66">
-        <v>100</v>
-      </c>
       <c r="L66">
         <v>100</v>
       </c>
       <c r="M66">
+        <v>100</v>
+      </c>
+      <c r="N66">
         <v>70</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>75</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>55</v>
       </c>
-      <c r="Q66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4070,33 +4256,36 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L67">
         <v>100</v>
       </c>
       <c r="M67">
+        <v>100</v>
+      </c>
+      <c r="N67">
         <v>70</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>45</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>75</v>
       </c>
-      <c r="Q67">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R67">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C68">
         <v>62</v>
       </c>
@@ -4116,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="I68">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J68">
         <v>100</v>
@@ -4125,30 +4314,33 @@
         <v>100</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
       <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
         <v>90</v>
       </c>
-      <c r="O68">
-        <v>100</v>
-      </c>
-      <c r="Q68">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="P68">
+        <v>100</v>
       </c>
       <c r="R68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C69">
         <v>63</v>
       </c>
@@ -4182,19 +4374,22 @@
       <c r="M69">
         <v>0</v>
       </c>
-      <c r="Q69">
-        <f t="shared" si="0"/>
+      <c r="N69">
         <v>0</v>
       </c>
       <c r="R69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C70">
         <v>64</v>
       </c>
@@ -4214,39 +4409,42 @@
         <v>50</v>
       </c>
       <c r="I70">
+        <v>90</v>
+      </c>
+      <c r="J70">
         <v>40</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>85</v>
       </c>
-      <c r="K70">
-        <v>100</v>
-      </c>
       <c r="L70">
         <v>100</v>
       </c>
       <c r="M70">
+        <v>100</v>
+      </c>
+      <c r="N70">
         <v>70</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>75</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>70</v>
       </c>
-      <c r="Q70">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C71">
         <v>65</v>
       </c>
@@ -4269,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -4278,27 +4476,30 @@
         <v>100</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
         <v>60</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>65</v>
       </c>
-      <c r="Q71">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="R71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4324,39 +4525,42 @@
         <v>100</v>
       </c>
       <c r="I72">
+        <v>90</v>
+      </c>
+      <c r="J72">
         <v>75</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>85</v>
       </c>
-      <c r="K72">
-        <v>100</v>
-      </c>
       <c r="L72">
         <v>100</v>
       </c>
       <c r="M72">
+        <v>100</v>
+      </c>
+      <c r="N72">
         <v>70</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>90</v>
       </c>
-      <c r="O72">
-        <v>100</v>
-      </c>
-      <c r="Q72">
-        <f t="shared" ref="Q72:Q79" si="2">IF(N72&gt;0,1,0)</f>
-        <v>1</v>
+      <c r="P72">
+        <v>100</v>
       </c>
       <c r="R72">
-        <f t="shared" ref="R72:R79" si="3">IF(O72&gt;0,1,0)</f>
+        <f t="shared" ref="R72:R79" si="2">IF(O72&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="S72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" ref="S72:S79" si="3">IF(P72&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C73">
         <v>67</v>
       </c>
@@ -4390,22 +4594,25 @@
       <c r="M73">
         <v>100</v>
       </c>
-      <c r="O73">
-        <v>100</v>
-      </c>
-      <c r="Q73">
+      <c r="N73">
+        <v>100</v>
+      </c>
+      <c r="P73">
+        <v>100</v>
+      </c>
+      <c r="R73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R73">
+      <c r="S73">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C74">
         <v>68</v>
       </c>
@@ -4425,11 +4632,11 @@
         <v>100</v>
       </c>
       <c r="I74">
+        <v>100</v>
+      </c>
+      <c r="J74">
         <v>85</v>
       </c>
-      <c r="J74">
-        <v>100</v>
-      </c>
       <c r="K74">
         <v>100</v>
       </c>
@@ -4437,27 +4644,30 @@
         <v>100</v>
       </c>
       <c r="M74">
+        <v>100</v>
+      </c>
+      <c r="N74">
         <v>90</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>95</v>
       </c>
-      <c r="O74">
+      <c r="P74">
         <v>85</v>
       </c>
-      <c r="Q74">
+      <c r="R74">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R74">
+      <c r="S74">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C75">
         <v>69</v>
       </c>
@@ -4477,39 +4687,42 @@
         <v>100</v>
       </c>
       <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
         <v>85</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>75</v>
       </c>
-      <c r="K75">
-        <v>100</v>
-      </c>
       <c r="L75">
         <v>100</v>
       </c>
       <c r="M75">
+        <v>100</v>
+      </c>
+      <c r="N75">
         <v>50</v>
       </c>
-      <c r="N75">
+      <c r="O75">
         <v>90</v>
       </c>
-      <c r="O75">
+      <c r="P75">
         <v>70</v>
       </c>
-      <c r="Q75">
+      <c r="R75">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R75">
+      <c r="S75">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4535,36 +4748,39 @@
         <v>100</v>
       </c>
       <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
         <v>85</v>
       </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
       <c r="K76">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L76">
         <v>100</v>
       </c>
       <c r="M76">
+        <v>100</v>
+      </c>
+      <c r="N76">
         <v>50</v>
       </c>
-      <c r="O76">
+      <c r="P76">
         <v>20</v>
       </c>
-      <c r="Q76">
+      <c r="R76">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R76">
+      <c r="S76">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C77">
         <v>71</v>
       </c>
@@ -4587,30 +4803,33 @@
         <v>0</v>
       </c>
       <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
         <v>50</v>
       </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77">
         <v>0</v>
       </c>
-      <c r="Q77">
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="R77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R77">
+      <c r="S77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
         <v>79</v>
       </c>
@@ -4653,19 +4872,22 @@
       <c r="O78">
         <v>100</v>
       </c>
-      <c r="Q78">
+      <c r="P78">
+        <v>100</v>
+      </c>
+      <c r="R78">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R78">
+      <c r="S78">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
         <v>79</v>
       </c>
@@ -4688,10 +4910,10 @@
         <v>50</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J79">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -4703,51 +4925,82 @@
         <v>100</v>
       </c>
       <c r="N79">
+        <v>100</v>
+      </c>
+      <c r="O79">
         <v>85</v>
       </c>
-      <c r="Q79">
+      <c r="R79">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R79">
+      <c r="S79">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C80" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9"/>
-      <c r="K80" s="9"/>
-      <c r="L80" s="9"/>
-      <c r="M80" s="9"/>
+      <c r="F80" s="10">
+        <f t="shared" ref="F80:N80" si="4">COUNTIF(F7:F79,"&gt;0")</f>
+        <v>49</v>
+      </c>
+      <c r="G80" s="10">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="H80" s="10">
+        <f t="shared" si="4"/>
+        <v>59</v>
+      </c>
+      <c r="I80" s="10">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="J80" s="10">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="K80" s="10">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L80" s="10">
+        <f t="shared" si="4"/>
+        <v>58</v>
+      </c>
+      <c r="M80" s="10">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
       <c r="N80" s="10">
-        <f>COUNTIF(N7:N79,"&gt;0")</f>
+        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="O80" s="10">
+        <f>COUNTIF(O7:O79,"&gt;0")</f>
         <v>50</v>
       </c>
-      <c r="O80" s="11">
-        <f>COUNTIF(O7:O79,"&gt;0")</f>
+      <c r="P80" s="11">
+        <f>COUNTIF(P7:P79,"&gt;0")</f>
         <v>60</v>
       </c>
-      <c r="P80" s="9"/>
       <c r="Q80" s="9"/>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
-      <c r="T80" s="12"/>
+      <c r="T80" s="9"/>
+      <c r="U80" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="T4:U4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
